--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/68.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/68.xlsx
@@ -426,13 +426,13 @@
         <v>-7.572312043012498</v>
       </c>
       <c r="E2">
-        <v>-10.15982823729838</v>
+        <v>-14.75958495432348</v>
       </c>
       <c r="F2">
-        <v>-0.7184837856982561</v>
+        <v>-0.422247176946111</v>
       </c>
       <c r="G2">
-        <v>-6.051303161440728</v>
+        <v>-9.694203929718356</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-7.518204912662187</v>
       </c>
       <c r="E3">
-        <v>-10.30238459905984</v>
+        <v>-14.11300037856029</v>
       </c>
       <c r="F3">
-        <v>-0.2995568525500734</v>
+        <v>-0.4250470587675733</v>
       </c>
       <c r="G3">
-        <v>-7.226928752752616</v>
+        <v>-9.858698128936439</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-7.39336470595519</v>
       </c>
       <c r="E4">
-        <v>-10.89409765527209</v>
+        <v>-15.11773290664211</v>
       </c>
       <c r="F4">
-        <v>-0.4248341683450538</v>
+        <v>0.1502888939076009</v>
       </c>
       <c r="G4">
-        <v>-7.088674482345413</v>
+        <v>-10.22726134060107</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-7.209225945352213</v>
       </c>
       <c r="E5">
-        <v>-12.13382628503395</v>
+        <v>-14.73755392827616</v>
       </c>
       <c r="F5">
-        <v>-0.2166886343088164</v>
+        <v>-0.5681748637254802</v>
       </c>
       <c r="G5">
-        <v>-6.68905450862064</v>
+        <v>-9.668370872380848</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-6.967038149050285</v>
       </c>
       <c r="E6">
-        <v>-12.47995566733623</v>
+        <v>-14.97389045826247</v>
       </c>
       <c r="F6">
-        <v>-0.2817038782849384</v>
+        <v>-0.1435081728432997</v>
       </c>
       <c r="G6">
-        <v>-6.895922403057392</v>
+        <v>-9.796253201438647</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-6.677812953538687</v>
       </c>
       <c r="E7">
-        <v>-12.46387052766098</v>
+        <v>-15.90541567553629</v>
       </c>
       <c r="F7">
-        <v>-0.271293785133957</v>
+        <v>0.5107173494374855</v>
       </c>
       <c r="G7">
-        <v>-7.420337076352525</v>
+        <v>-8.644944743103803</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-6.352128678661508</v>
       </c>
       <c r="E8">
-        <v>-13.54954952862991</v>
+        <v>-17.15011656975857</v>
       </c>
       <c r="F8">
-        <v>0.001549728163130123</v>
+        <v>0.3236388551892451</v>
       </c>
       <c r="G8">
-        <v>-6.454279824820812</v>
+        <v>-9.222016459984905</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-6.007054978040217</v>
       </c>
       <c r="E9">
-        <v>-14.90599051899146</v>
+        <v>-18.10286674470635</v>
       </c>
       <c r="F9">
-        <v>-0.2299756474497205</v>
+        <v>0.3904425443880112</v>
       </c>
       <c r="G9">
-        <v>-6.401242159533948</v>
+        <v>-8.75806813758722</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-5.661592481702437</v>
       </c>
       <c r="E10">
-        <v>-14.16239244456195</v>
+        <v>-19.05638676023543</v>
       </c>
       <c r="F10">
-        <v>-0.1734503409848906</v>
+        <v>0.6918349118551805</v>
       </c>
       <c r="G10">
-        <v>-5.290154915074778</v>
+        <v>-9.357803251779405</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-5.333151309653288</v>
       </c>
       <c r="E11">
-        <v>-15.27952169751415</v>
+        <v>-19.26319311121771</v>
       </c>
       <c r="F11">
-        <v>-0.2265669155872005</v>
+        <v>1.051487187128642</v>
       </c>
       <c r="G11">
-        <v>-4.923183095866481</v>
+        <v>-9.974118378511466</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-5.042412991718598</v>
       </c>
       <c r="E12">
-        <v>-16.4156343135065</v>
+        <v>-20.08763803210616</v>
       </c>
       <c r="F12">
-        <v>-0.2017357743208825</v>
+        <v>0.7167654572098344</v>
       </c>
       <c r="G12">
-        <v>-4.583957286164848</v>
+        <v>-8.509748571190002</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-4.805128308420705</v>
       </c>
       <c r="E13">
-        <v>-17.20687646297071</v>
+        <v>-20.9840992751386</v>
       </c>
       <c r="F13">
-        <v>0.2969703950235178</v>
+        <v>0.5016111065785105</v>
       </c>
       <c r="G13">
-        <v>-4.712715701379018</v>
+        <v>-7.009495324894452</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-4.642589442095214</v>
       </c>
       <c r="E14">
-        <v>-18.65450280595071</v>
+        <v>-22.69759232710892</v>
       </c>
       <c r="F14">
-        <v>0.312359804632727</v>
+        <v>0.7201070913127277</v>
       </c>
       <c r="G14">
-        <v>-3.962116582326683</v>
+        <v>-5.972307752397096</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-4.560825689707594</v>
       </c>
       <c r="E15">
-        <v>-18.36175507525085</v>
+        <v>-23.67190256680722</v>
       </c>
       <c r="F15">
-        <v>0.671972318270854</v>
+        <v>0.9520400236877556</v>
       </c>
       <c r="G15">
-        <v>-4.090694530355083</v>
+        <v>-5.761243175585816</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-4.568267177247961</v>
       </c>
       <c r="E16">
-        <v>-20.11431074401134</v>
+        <v>-22.93513343118127</v>
       </c>
       <c r="F16">
-        <v>0.477240537588149</v>
+        <v>1.328673830718607</v>
       </c>
       <c r="G16">
-        <v>-3.264053101662617</v>
+        <v>-6.99431967518202</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-4.664338995352313</v>
       </c>
       <c r="E17">
-        <v>-19.59047951317407</v>
+        <v>-23.72941871517864</v>
       </c>
       <c r="F17">
-        <v>0.4280918428452488</v>
+        <v>1.029195820319307</v>
       </c>
       <c r="G17">
-        <v>-3.14142072709993</v>
+        <v>-5.813585221902077</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-4.848786980301851</v>
       </c>
       <c r="E18">
-        <v>-22.02903559546052</v>
+        <v>-24.64126318441512</v>
       </c>
       <c r="F18">
-        <v>0.9951929951691931</v>
+        <v>1.96486662300785</v>
       </c>
       <c r="G18">
-        <v>-2.479142248763168</v>
+        <v>-6.077835118970398</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-5.112220185590204</v>
       </c>
       <c r="E19">
-        <v>-22.05823972433598</v>
+        <v>-24.32302467352609</v>
       </c>
       <c r="F19">
-        <v>0.9139301529545616</v>
+        <v>1.171386741744648</v>
       </c>
       <c r="G19">
-        <v>-2.438018698958647</v>
+        <v>-6.069592690413073</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-5.443664896688319</v>
       </c>
       <c r="E20">
-        <v>-23.28686000735703</v>
+        <v>-26.07911255201256</v>
       </c>
       <c r="F20">
-        <v>1.259705617496326</v>
+        <v>1.949399346862777</v>
       </c>
       <c r="G20">
-        <v>-1.979248144181766</v>
+        <v>-4.333160397490251</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-5.832087782968049</v>
       </c>
       <c r="E21">
-        <v>-22.28932322447339</v>
+        <v>-27.23295414374494</v>
       </c>
       <c r="F21">
-        <v>1.488316796586128</v>
+        <v>2.493850449291975</v>
       </c>
       <c r="G21">
-        <v>-2.475044003035422</v>
+        <v>-4.487692808053859</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-6.263828461776456</v>
       </c>
       <c r="E22">
-        <v>-24.06454390564227</v>
+        <v>-26.84635831771013</v>
       </c>
       <c r="F22">
-        <v>1.554506665539419</v>
+        <v>1.545286936346261</v>
       </c>
       <c r="G22">
-        <v>-1.778145356024958</v>
+        <v>-4.169535721985421</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-6.72567068683866</v>
       </c>
       <c r="E23">
-        <v>-24.81356709193297</v>
+        <v>-27.72623628892647</v>
       </c>
       <c r="F23">
-        <v>1.321718858004702</v>
+        <v>2.478321873959095</v>
       </c>
       <c r="G23">
-        <v>-1.484617118981713</v>
+        <v>-6.073097035038559</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-7.197461510117741</v>
       </c>
       <c r="E24">
-        <v>-25.10505137838469</v>
+        <v>-28.26424617188176</v>
       </c>
       <c r="F24">
-        <v>1.878679964950978</v>
+        <v>2.299381261075957</v>
       </c>
       <c r="G24">
-        <v>-2.510235104260466</v>
+        <v>-5.128210225008384</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-7.667718865695596</v>
       </c>
       <c r="E25">
-        <v>-24.78209419757966</v>
+        <v>-27.65650231768235</v>
       </c>
       <c r="F25">
-        <v>1.873368473164227</v>
+        <v>2.549858026130055</v>
       </c>
       <c r="G25">
-        <v>-1.461819191586691</v>
+        <v>-4.734706448270417</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-8.120841164852928</v>
       </c>
       <c r="E26">
-        <v>-25.09196861697653</v>
+        <v>-29.06485773406784</v>
       </c>
       <c r="F26">
-        <v>1.442035909791719</v>
+        <v>2.640776318791717</v>
       </c>
       <c r="G26">
-        <v>-2.267687206586313</v>
+        <v>-3.767671392713989</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-8.546321775688366</v>
       </c>
       <c r="E27">
-        <v>-24.40080121460783</v>
+        <v>-28.38170573069271</v>
       </c>
       <c r="F27">
-        <v>1.761542187255905</v>
+        <v>2.925791034338137</v>
       </c>
       <c r="G27">
-        <v>-2.168171037909914</v>
+        <v>-4.973989530492923</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-8.926883401750478</v>
       </c>
       <c r="E28">
-        <v>-25.41906482302457</v>
+        <v>-28.88414445031774</v>
       </c>
       <c r="F28">
-        <v>1.637408018476788</v>
+        <v>2.315232899695928</v>
       </c>
       <c r="G28">
-        <v>-1.858574658890067</v>
+        <v>-4.499058959535776</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-9.254541180385365</v>
       </c>
       <c r="E29">
-        <v>-24.78057263031309</v>
+        <v>-28.76638601222228</v>
       </c>
       <c r="F29">
-        <v>1.97725899935373</v>
+        <v>3.115493796518447</v>
       </c>
       <c r="G29">
-        <v>-1.773617270272925</v>
+        <v>-4.360456879643271</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-9.520495437353299</v>
       </c>
       <c r="E30">
-        <v>-23.36905181059624</v>
+        <v>-29.14685934139873</v>
       </c>
       <c r="F30">
-        <v>1.974430953040573</v>
+        <v>2.52976514640775</v>
       </c>
       <c r="G30">
-        <v>-2.469977796947639</v>
+        <v>-4.515921157129762</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-9.718590199480232</v>
       </c>
       <c r="E31">
-        <v>-24.69474899091972</v>
+        <v>-27.99153693866584</v>
       </c>
       <c r="F31">
-        <v>1.956587919184271</v>
+        <v>1.980320645274477</v>
       </c>
       <c r="G31">
-        <v>-1.747370779018927</v>
+        <v>-5.443755458715504</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-9.842919493728468</v>
       </c>
       <c r="E32">
-        <v>-24.31910301503545</v>
+        <v>-27.44923859082529</v>
       </c>
       <c r="F32">
-        <v>1.724862078659943</v>
+        <v>2.433374658683194</v>
       </c>
       <c r="G32">
-        <v>-2.618836975434967</v>
+        <v>-4.319681139324052</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-9.888568777412399</v>
       </c>
       <c r="E33">
-        <v>-23.8027211239408</v>
+        <v>-27.97939157137727</v>
       </c>
       <c r="F33">
-        <v>1.868966528785751</v>
+        <v>2.641492028227736</v>
       </c>
       <c r="G33">
-        <v>-2.82511096876946</v>
+        <v>-4.891919616848091</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-9.857999009135504</v>
       </c>
       <c r="E34">
-        <v>-22.83535303489626</v>
+        <v>-26.64473706946662</v>
       </c>
       <c r="F34">
-        <v>1.582102897196282</v>
+        <v>1.731901544848933</v>
       </c>
       <c r="G34">
-        <v>-3.086722763703987</v>
+        <v>-5.316860777347098</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-9.752884716587142</v>
       </c>
       <c r="E35">
-        <v>-22.41947609592785</v>
+        <v>-27.06120271005603</v>
       </c>
       <c r="F35">
-        <v>1.626448717737751</v>
+        <v>2.657245919494177</v>
       </c>
       <c r="G35">
-        <v>-3.292996757038479</v>
+        <v>-6.624217570606013</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-9.585277282441151</v>
       </c>
       <c r="E36">
-        <v>-21.52766559570129</v>
+        <v>-26.81299704969562</v>
       </c>
       <c r="F36">
-        <v>1.505571689586441</v>
+        <v>2.005807853523812</v>
       </c>
       <c r="G36">
-        <v>-3.372858408573804</v>
+        <v>-7.026688925865942</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-9.360615322347353</v>
       </c>
       <c r="E37">
-        <v>-21.71792943113356</v>
+        <v>-26.55893154396928</v>
       </c>
       <c r="F37">
-        <v>1.791224248033017</v>
+        <v>2.381089764953295</v>
       </c>
       <c r="G37">
-        <v>-3.131960965344051</v>
+        <v>-5.442964684319677</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-9.092559534615551</v>
       </c>
       <c r="E38">
-        <v>-21.16991614909534</v>
+        <v>-25.67145479336807</v>
       </c>
       <c r="F38">
-        <v>1.779019082720169</v>
+        <v>2.326140841655993</v>
       </c>
       <c r="G38">
-        <v>-4.305696573037698</v>
+        <v>-6.932422711684655</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-8.789989602450785</v>
       </c>
       <c r="E39">
-        <v>-21.25688549241264</v>
+        <v>-24.36863999220535</v>
       </c>
       <c r="F39">
-        <v>2.18084851267457</v>
+        <v>2.835991037670254</v>
       </c>
       <c r="G39">
-        <v>-4.435951225282976</v>
+        <v>-7.161737442809568</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-8.468906714113906</v>
       </c>
       <c r="E40">
-        <v>-18.88847094403101</v>
+        <v>-24.94778653304632</v>
       </c>
       <c r="F40">
-        <v>2.023735380855199</v>
+        <v>2.654644845849387</v>
       </c>
       <c r="G40">
-        <v>-4.193633013117983</v>
+        <v>-6.55746768042223</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-8.14125816869154</v>
       </c>
       <c r="E41">
-        <v>-19.98668928952718</v>
+        <v>-24.21429148412792</v>
       </c>
       <c r="F41">
-        <v>2.108318319620251</v>
+        <v>3.106961612269612</v>
       </c>
       <c r="G41">
-        <v>-5.201397871891798</v>
+        <v>-6.844446599232824</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-7.818969103079938</v>
       </c>
       <c r="E42">
-        <v>-18.31438270865661</v>
+        <v>-24.21138420381499</v>
       </c>
       <c r="F42">
-        <v>1.993369088603375</v>
+        <v>2.596679008471089</v>
       </c>
       <c r="G42">
-        <v>-5.259032528583445</v>
+        <v>-7.079555967631716</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-7.511787771855838</v>
       </c>
       <c r="E43">
-        <v>-17.03440500191458</v>
+        <v>-22.36645672224604</v>
       </c>
       <c r="F43">
-        <v>2.285863961797075</v>
+        <v>2.5280636797624</v>
       </c>
       <c r="G43">
-        <v>-5.058290674798177</v>
+        <v>-8.490353270552125</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-7.22671611013187</v>
       </c>
       <c r="E44">
-        <v>-17.55556896156133</v>
+        <v>-23.7002915703613</v>
       </c>
       <c r="F44">
-        <v>2.272871847451567</v>
+        <v>2.698637781877263</v>
       </c>
       <c r="G44">
-        <v>-4.938394839016066</v>
+        <v>-7.264639832135314</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-6.971641240891779</v>
       </c>
       <c r="E45">
-        <v>-17.27362164136976</v>
+        <v>-22.26133272663198</v>
       </c>
       <c r="F45">
-        <v>2.591859566921601</v>
+        <v>2.372656984792796</v>
       </c>
       <c r="G45">
-        <v>-4.996324805648063</v>
+        <v>-8.575268003288995</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-6.744416418649945</v>
       </c>
       <c r="E46">
-        <v>-16.654443390301</v>
+        <v>-18.23068745204685</v>
       </c>
       <c r="F46">
-        <v>2.912959623268773</v>
+        <v>2.923829460328308</v>
       </c>
       <c r="G46">
-        <v>-5.278303142802064</v>
+        <v>-8.559800324857772</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-6.544191067594882</v>
       </c>
       <c r="E47">
-        <v>-15.50846775791994</v>
+        <v>-20.69205345790993</v>
       </c>
       <c r="F47">
-        <v>2.208858928032833</v>
+        <v>2.286531625923731</v>
       </c>
       <c r="G47">
-        <v>-4.389968186348917</v>
+        <v>-7.288405719890372</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-6.363389230762646</v>
       </c>
       <c r="E48">
-        <v>-14.34717229797093</v>
+        <v>-18.71240387461279</v>
       </c>
       <c r="F48">
-        <v>2.675590943996575</v>
+        <v>2.647386690666057</v>
       </c>
       <c r="G48">
-        <v>-5.769075451448209</v>
+        <v>-6.279374309594611</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-6.202315167070317</v>
       </c>
       <c r="E49">
-        <v>-14.4116849386842</v>
+        <v>-17.60946233072661</v>
       </c>
       <c r="F49">
-        <v>2.06240357121788</v>
+        <v>2.244655996977411</v>
       </c>
       <c r="G49">
-        <v>-5.411770110954037</v>
+        <v>-7.797506932167576</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-6.052129147737058</v>
       </c>
       <c r="E50">
-        <v>-13.70462712102258</v>
+        <v>-18.79071930410144</v>
       </c>
       <c r="F50">
-        <v>2.318296202351481</v>
+        <v>2.702469809482613</v>
       </c>
       <c r="G50">
-        <v>-5.396532118031976</v>
+        <v>-8.014599112983557</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-5.906997028496805</v>
       </c>
       <c r="E51">
-        <v>-11.85438321096863</v>
+        <v>-18.14573780813696</v>
       </c>
       <c r="F51">
-        <v>2.458999375921394</v>
+        <v>2.563658627060695</v>
       </c>
       <c r="G51">
-        <v>-5.835041129679286</v>
+        <v>-9.259077857498832</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-5.758573218813147</v>
       </c>
       <c r="E52">
-        <v>-11.52415782938129</v>
+        <v>-17.66598674329036</v>
       </c>
       <c r="F52">
-        <v>2.816038980406426</v>
+        <v>2.363559853975252</v>
       </c>
       <c r="G52">
-        <v>-5.270835082532767</v>
+        <v>-7.606438119539551</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-5.603136026772014</v>
       </c>
       <c r="E53">
-        <v>-11.65923768055609</v>
+        <v>-14.91799097511178</v>
       </c>
       <c r="F53">
-        <v>2.406528927893268</v>
+        <v>2.448699455634985</v>
       </c>
       <c r="G53">
-        <v>-5.496159848241396</v>
+        <v>-7.782328001233585</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-5.437932871831725</v>
       </c>
       <c r="E54">
-        <v>-10.39294049379123</v>
+        <v>-15.65055768685861</v>
       </c>
       <c r="F54">
-        <v>2.314608310674218</v>
+        <v>3.00049983366182</v>
       </c>
       <c r="G54">
-        <v>-5.959550362973975</v>
+        <v>-8.307221732876396</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-5.259424933062328</v>
       </c>
       <c r="E55">
-        <v>-10.11353364751796</v>
+        <v>-14.47963469116929</v>
       </c>
       <c r="F55">
-        <v>2.145104459243772</v>
+        <v>2.578279311720106</v>
       </c>
       <c r="G55">
-        <v>-5.444388734476477</v>
+        <v>-7.311141304075765</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-5.066981204070538</v>
       </c>
       <c r="E56">
-        <v>-9.540274122886974</v>
+        <v>-15.56298152802427</v>
       </c>
       <c r="F56">
-        <v>2.197331367255475</v>
+        <v>2.050953876976386</v>
       </c>
       <c r="G56">
-        <v>-5.96886246975968</v>
+        <v>-7.982692514539517</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-4.859424394411849</v>
       </c>
       <c r="E57">
-        <v>-7.793392632058096</v>
+        <v>-13.57445160719809</v>
       </c>
       <c r="F57">
-        <v>2.285815916487712</v>
+        <v>2.357169827830056</v>
       </c>
       <c r="G57">
-        <v>-6.508157482826894</v>
+        <v>-8.443963360144696</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-4.642747765900308</v>
       </c>
       <c r="E58">
-        <v>-8.236476642864593</v>
+        <v>-14.07167805324029</v>
       </c>
       <c r="F58">
-        <v>1.751285342074442</v>
+        <v>2.453702794747894</v>
       </c>
       <c r="G58">
-        <v>-5.513678290147271</v>
+        <v>-8.092964527487776</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-4.418069459228602</v>
       </c>
       <c r="E59">
-        <v>-8.900042996156547</v>
+        <v>-13.56727850436994</v>
       </c>
       <c r="F59">
-        <v>2.16276028206704</v>
+        <v>2.165452476126139</v>
       </c>
       <c r="G59">
-        <v>-6.348201213025524</v>
+        <v>-7.721697589258166</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-4.190237030183609</v>
       </c>
       <c r="E60">
-        <v>-8.00849061894843</v>
+        <v>-12.54394753353862</v>
       </c>
       <c r="F60">
-        <v>1.599815049002941</v>
+        <v>2.040642359546337</v>
       </c>
       <c r="G60">
-        <v>-6.862585192013434</v>
+        <v>-8.308412816302475</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-3.962230035766126</v>
       </c>
       <c r="E61">
-        <v>-6.733788584425332</v>
+        <v>-11.7478055751981</v>
       </c>
       <c r="F61">
-        <v>1.504935503421091</v>
+        <v>2.071876780836295</v>
       </c>
       <c r="G61">
-        <v>-5.957516005607119</v>
+        <v>-8.871358874370168</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-3.741691832662594</v>
       </c>
       <c r="E62">
-        <v>-6.039061801486599</v>
+        <v>-12.60115121720351</v>
       </c>
       <c r="F62">
-        <v>1.755327775000104</v>
+        <v>1.964815264228876</v>
       </c>
       <c r="G62">
-        <v>-5.644553093267283</v>
+        <v>-8.504839863737073</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-3.532500392462978</v>
       </c>
       <c r="E63">
-        <v>-6.913700328276067</v>
+        <v>-11.73641646306881</v>
       </c>
       <c r="F63">
-        <v>2.036006815560271</v>
+        <v>2.446459550177815</v>
       </c>
       <c r="G63">
-        <v>-6.095051688492805</v>
+        <v>-9.485898860238567</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-3.337279559157031</v>
       </c>
       <c r="E64">
-        <v>-5.842852079682258</v>
+        <v>-10.93537922432601</v>
       </c>
       <c r="F64">
-        <v>1.595752735259612</v>
+        <v>2.3245155848117</v>
       </c>
       <c r="G64">
-        <v>-5.662061691508479</v>
+        <v>-8.419311542568588</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-3.156791207621011</v>
       </c>
       <c r="E65">
-        <v>-5.423510858097975</v>
+        <v>-12.41372673497405</v>
       </c>
       <c r="F65">
-        <v>1.656226869133587</v>
+        <v>2.328574585085417</v>
       </c>
       <c r="G65">
-        <v>-6.343223599919846</v>
+        <v>-8.185330914386144</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-2.991641353684878</v>
       </c>
       <c r="E66">
-        <v>-4.550271629776877</v>
+        <v>-10.27348387794289</v>
       </c>
       <c r="F66">
-        <v>1.592971077521012</v>
+        <v>1.889851327745132</v>
       </c>
       <c r="G66">
-        <v>-5.433609921653701</v>
+        <v>-8.113826534162726</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-2.843473251527048</v>
       </c>
       <c r="E67">
-        <v>-4.464724227297976</v>
+        <v>-11.79002453837161</v>
       </c>
       <c r="F67">
-        <v>1.336505216144673</v>
+        <v>1.742880726405638</v>
       </c>
       <c r="G67">
-        <v>-5.680269189941838</v>
+        <v>-8.163455010249326</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-2.710202448800946</v>
       </c>
       <c r="E68">
-        <v>-4.93658669042322</v>
+        <v>-11.42987500054159</v>
       </c>
       <c r="F68">
-        <v>1.236574286140552</v>
+        <v>1.848956485803726</v>
       </c>
       <c r="G68">
-        <v>-5.530386270327964</v>
+        <v>-7.245323280814863</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-2.590608393417177</v>
       </c>
       <c r="E69">
-        <v>-5.077354304951653</v>
+        <v>-10.31385975219528</v>
       </c>
       <c r="F69">
-        <v>1.307601820726193</v>
+        <v>1.577647937304026</v>
       </c>
       <c r="G69">
-        <v>-4.93057568803991</v>
+        <v>-8.152223388851347</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-2.481208973922683</v>
       </c>
       <c r="E70">
-        <v>-5.65670462712296</v>
+        <v>-10.16003654710273</v>
       </c>
       <c r="F70">
-        <v>1.248661823282203</v>
+        <v>1.848517451080242</v>
       </c>
       <c r="G70">
-        <v>-4.799520417734128</v>
+        <v>-6.734847236704251</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-2.383051083668228</v>
       </c>
       <c r="E71">
-        <v>-5.127715464390954</v>
+        <v>-9.834099630400658</v>
       </c>
       <c r="F71">
-        <v>0.6731850481485525</v>
+        <v>2.03423410931828</v>
       </c>
       <c r="G71">
-        <v>-3.748026719237594</v>
+        <v>-7.605758906676746</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-2.293226201353402</v>
       </c>
       <c r="E72">
-        <v>-4.672821193372452</v>
+        <v>-10.18789571919792</v>
       </c>
       <c r="F72">
-        <v>0.9322055945951243</v>
+        <v>1.631137277237596</v>
       </c>
       <c r="G72">
-        <v>-4.170185403854191</v>
+        <v>-7.979578635279604</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-2.211207332228249</v>
       </c>
       <c r="E73">
-        <v>-5.928662133653603</v>
+        <v>-10.54707163511629</v>
       </c>
       <c r="F73">
-        <v>1.071689411348116</v>
+        <v>1.824971936023069</v>
       </c>
       <c r="G73">
-        <v>-3.546261124325778</v>
+        <v>-6.993181091300893</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-2.136232869179639</v>
       </c>
       <c r="E74">
-        <v>-4.299539080920185</v>
+        <v>-9.828588477533323</v>
       </c>
       <c r="F74">
-        <v>0.8380450719189045</v>
+        <v>1.218999643322758</v>
       </c>
       <c r="G74">
-        <v>-3.574758533569556</v>
+        <v>-7.395396511279186</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-2.070484999231871</v>
       </c>
       <c r="E75">
-        <v>-4.665448837687965</v>
+        <v>-11.03483357048247</v>
       </c>
       <c r="F75">
-        <v>0.6099342267403934</v>
+        <v>0.618661905696289</v>
       </c>
       <c r="G75">
-        <v>-3.198933978593877</v>
+        <v>-7.551188910921621</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-2.01594297088759</v>
       </c>
       <c r="E76">
-        <v>-4.813421254362601</v>
+        <v>-9.30463044942384</v>
       </c>
       <c r="F76">
-        <v>0.3038541281407817</v>
+        <v>1.413535100930999</v>
       </c>
       <c r="G76">
-        <v>-3.472292546711216</v>
+        <v>-7.431837757918379</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-1.974599153818706</v>
       </c>
       <c r="E77">
-        <v>-6.005007676948918</v>
+        <v>-11.36554802726264</v>
       </c>
       <c r="F77">
-        <v>0.1868654565782131</v>
+        <v>0.810402451687485</v>
       </c>
       <c r="G77">
-        <v>-3.50110823444626</v>
+        <v>-6.524937649881895</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-1.950401317253057</v>
       </c>
       <c r="E78">
-        <v>-5.957762107626893</v>
+        <v>-11.38206790044262</v>
       </c>
       <c r="F78">
-        <v>0.6085276588904399</v>
+        <v>1.111499091991855</v>
       </c>
       <c r="G78">
-        <v>-3.372090602728893</v>
+        <v>-6.025319167911485</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-1.947353361449552</v>
       </c>
       <c r="E79">
-        <v>-6.885732472804695</v>
+        <v>-11.90742069854646</v>
       </c>
       <c r="F79">
-        <v>0.02614561308705304</v>
+        <v>1.288100395329487</v>
       </c>
       <c r="G79">
-        <v>-1.248142762414092</v>
+        <v>-6.566546820477213</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-1.971932502763778</v>
       </c>
       <c r="E80">
-        <v>-7.263633628744786</v>
+        <v>-12.73647560597472</v>
       </c>
       <c r="F80">
-        <v>0.1770965197969986</v>
+        <v>0.6204379254078911</v>
       </c>
       <c r="G80">
-        <v>-1.70392084312876</v>
+        <v>-5.534845450427248</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-2.026951658524176</v>
       </c>
       <c r="E81">
-        <v>-7.147899418530755</v>
+        <v>-13.05010865879795</v>
       </c>
       <c r="F81">
-        <v>-0.2354652382280728</v>
+        <v>1.571276135241692</v>
       </c>
       <c r="G81">
-        <v>-0.6479515584251424</v>
+        <v>-5.812381013589761</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-2.120144289702466</v>
       </c>
       <c r="E82">
-        <v>-8.834484277947503</v>
+        <v>-14.24242416569951</v>
       </c>
       <c r="F82">
-        <v>-0.6889044424790914</v>
+        <v>0.7681391467966542</v>
       </c>
       <c r="G82">
-        <v>-1.494139223947221</v>
+        <v>-5.109034766214989</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-2.257449529152494</v>
       </c>
       <c r="E83">
-        <v>-8.432785991097104</v>
+        <v>-14.31322232833542</v>
       </c>
       <c r="F83">
-        <v>-0.1833965483903043</v>
+        <v>0.508149410488807</v>
       </c>
       <c r="G83">
-        <v>-0.7341295614623984</v>
+        <v>-6.560988431155513</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-2.446313162466355</v>
       </c>
       <c r="E84">
-        <v>-10.71520028959907</v>
+        <v>-16.50431994847272</v>
       </c>
       <c r="F84">
-        <v>-0.2475403498586812</v>
+        <v>0.6090478736193979</v>
       </c>
       <c r="G84">
-        <v>-0.4791294279701523</v>
+        <v>-5.274250834176149</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-2.688017003895805</v>
       </c>
       <c r="E85">
-        <v>-11.46605750786288</v>
+        <v>-14.89778039561555</v>
       </c>
       <c r="F85">
-        <v>-0.6512857936157574</v>
+        <v>0.6140255333428202</v>
       </c>
       <c r="G85">
-        <v>-0.1766204875187062</v>
+        <v>-4.512912276959751</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-2.986697835119317</v>
       </c>
       <c r="E86">
-        <v>-11.77860372692427</v>
+        <v>-16.53463808195407</v>
       </c>
       <c r="F86">
-        <v>-0.8640561028618244</v>
+        <v>-0.3248560213989731</v>
       </c>
       <c r="G86">
-        <v>-0.7189145370912532</v>
+        <v>-5.288386336654237</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-3.345223060617744</v>
       </c>
       <c r="E87">
-        <v>-12.87033276916745</v>
+        <v>-18.29291321338625</v>
       </c>
       <c r="F87">
-        <v>-0.9517354789785409</v>
+        <v>0.3188268689463828</v>
       </c>
       <c r="G87">
-        <v>-0.6062308262968028</v>
+        <v>-4.726598549797029</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-3.764211527288133</v>
       </c>
       <c r="E88">
-        <v>-14.12988705813489</v>
+        <v>-18.44997880586829</v>
       </c>
       <c r="F88">
-        <v>-0.9835654964311119</v>
+        <v>0.4039507316254627</v>
       </c>
       <c r="G88">
-        <v>-0.08259380251125839</v>
+        <v>-5.269748998196591</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-4.23991505848</v>
       </c>
       <c r="E89">
-        <v>-16.77581102218057</v>
+        <v>-20.39268509821085</v>
       </c>
       <c r="F89">
-        <v>-1.671099671978465</v>
+        <v>-0.5394512240334074</v>
       </c>
       <c r="G89">
-        <v>-0.9666500460508887</v>
+        <v>-4.457495726042289</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-4.764225221743527</v>
       </c>
       <c r="E90">
-        <v>-17.16403257038414</v>
+        <v>-23.78716581572445</v>
       </c>
       <c r="F90">
-        <v>-2.254018499858866</v>
+        <v>-0.8623215015203624</v>
       </c>
       <c r="G90">
-        <v>-0.9153514281905301</v>
+        <v>-5.248119185676732</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-5.333939623551691</v>
       </c>
       <c r="E91">
-        <v>-18.48727531779546</v>
+        <v>-23.39487769786199</v>
       </c>
       <c r="F91">
-        <v>-1.872494840049289</v>
+        <v>-0.8981715859787193</v>
       </c>
       <c r="G91">
-        <v>-0.04074182152054104</v>
+        <v>-4.667300313774744</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-5.941128956591573</v>
       </c>
       <c r="E92">
-        <v>-21.86113336467812</v>
+        <v>-24.39587876336149</v>
       </c>
       <c r="F92">
-        <v>-2.194833305663647</v>
+        <v>-1.108618324659934</v>
       </c>
       <c r="G92">
-        <v>-0.8057356595541604</v>
+        <v>-4.987977378000836</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-6.578145557098317</v>
       </c>
       <c r="E93">
-        <v>-23.12325529840791</v>
+        <v>-25.5911830631081</v>
       </c>
       <c r="F93">
-        <v>-2.544687651296796</v>
+        <v>-1.003194490407849</v>
       </c>
       <c r="G93">
-        <v>-0.4914504149258672</v>
+        <v>-5.720447747937239</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-7.226026707248377</v>
       </c>
       <c r="E94">
-        <v>-24.44600444215239</v>
+        <v>-28.41380808293308</v>
       </c>
       <c r="F94">
-        <v>-2.906274992823197</v>
+        <v>-1.648969836812676</v>
       </c>
       <c r="G94">
-        <v>-1.303670874864574</v>
+        <v>-5.515167964735259</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-7.877594891598258</v>
       </c>
       <c r="E95">
-        <v>-26.39726502189545</v>
+        <v>-30.52249200460479</v>
       </c>
       <c r="F95">
-        <v>-3.046583863509377</v>
+        <v>-1.412680520266326</v>
       </c>
       <c r="G95">
-        <v>-1.397743496973854</v>
+        <v>-5.265457160396838</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-8.520183924492802</v>
       </c>
       <c r="E96">
-        <v>-29.17060665909495</v>
+        <v>-31.24899508965534</v>
       </c>
       <c r="F96">
-        <v>-3.261607332091059</v>
+        <v>-1.615522846189841</v>
       </c>
       <c r="G96">
-        <v>-1.596214745439987</v>
+        <v>-6.032235982958794</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-9.139956812234868</v>
       </c>
       <c r="E97">
-        <v>-30.27026505932556</v>
+        <v>-34.73143009358291</v>
       </c>
       <c r="F97">
-        <v>-3.435761638120821</v>
+        <v>-1.919629773635984</v>
       </c>
       <c r="G97">
-        <v>-2.610633921536356</v>
+        <v>-7.302140913338207</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-9.719951094185642</v>
       </c>
       <c r="E98">
-        <v>-33.01892424894626</v>
+        <v>-36.55388049441479</v>
       </c>
       <c r="F98">
-        <v>-3.524051521013401</v>
+        <v>-1.832339730198583</v>
       </c>
       <c r="G98">
-        <v>-2.443255528567521</v>
+        <v>-7.126533216698286</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-10.24015643533832</v>
       </c>
       <c r="E99">
-        <v>-36.09428113890232</v>
+        <v>-38.20451832715865</v>
       </c>
       <c r="F99">
-        <v>-3.866172228574014</v>
+        <v>-1.902678063105095</v>
       </c>
       <c r="G99">
-        <v>-2.974554204694369</v>
+        <v>-6.938525783785223</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-10.69219294891139</v>
       </c>
       <c r="E100">
-        <v>-37.68155656333085</v>
+        <v>-41.31542373807492</v>
       </c>
       <c r="F100">
-        <v>-4.208524050640007</v>
+        <v>-2.184041335139975</v>
       </c>
       <c r="G100">
-        <v>-4.088108927766241</v>
+        <v>-6.848160942038115</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-11.05290494740329</v>
       </c>
       <c r="E101">
-        <v>-39.86605166836497</v>
+        <v>-43.36696737471784</v>
       </c>
       <c r="F101">
-        <v>-4.371740593483205</v>
+        <v>-2.647215513108693</v>
       </c>
       <c r="G101">
-        <v>-3.489151463083644</v>
+        <v>-7.570961552038835</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-11.32304066315938</v>
       </c>
       <c r="E102">
-        <v>-40.7355390559707</v>
+        <v>-44.98473754311403</v>
       </c>
       <c r="F102">
-        <v>-4.227955064807476</v>
+        <v>-2.928780078422454</v>
       </c>
       <c r="G102">
-        <v>-4.443629283732077</v>
+        <v>-7.23080387541432</v>
       </c>
     </row>
   </sheetData>
